--- a/survey/output/required.xlsx
+++ b/survey/output/required.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Thứ hạng ước tính, Vị thế tương đối, Phân tích phổ điểm, So sánh tổ hợp</t>
+          <t>Vị thế tương đối, Phân tích phổ điểm, So sánh tổ hợp, Thứ hạng ước tính</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -469,11 +469,11 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Thứ hạng ước tính, Vị thế tương đối, Phân tích phổ điểm</t>
+          <t>Vị thế tương đối, Phân tích phổ điểm, Thứ hạng ước tính</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -493,11 +493,11 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Thứ hạng ước tính, Phân tích phổ điểm, So sánh tổ hợp</t>
+          <t>Phân tích phổ điểm, So sánh tổ hợp, Thứ hạng ước tính</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Thứ hạng ước tính, Vị thế tương đối, So sánh tổ hợp</t>
+          <t>Vị thế tương đối, Thứ hạng ước tính, So sánh tổ hợp</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -541,11 +541,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Thứ hạng ước tính, Vị thế tương đối, Xác suất "an toàn", So sánh tổ hợp</t>
+          <t>Vị thế tương đối, Thứ hạng ước tính, Xác suất "an toàn", So sánh tổ hợp</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -613,7 +613,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Thứ hạng ước tính, Vị thế tương đối</t>
+          <t>Vị thế tương đối, Thứ hạng ước tính</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -661,11 +661,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Thứ hạng ước tính, Vị thế tương đối, So sánh tổ hợp</t>
+          <t>Vị thế tương đối, Thứ hạng ước tính, So sánh tổ hợp</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
